--- a/data/trans_bre/P19C08-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P19C08-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 0,79</t>
+          <t>-1,41; 0,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 0,07</t>
+          <t>-3,01; 0,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,0</t>
+          <t>-1,7; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,67</t>
+          <t>-0,95; 0,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 457,74</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 2,66</t>
+          <t>-0,59; 2,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,46</t>
+          <t>-0,91; 1,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,18</t>
+          <t>-0,44; 1,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-82,31; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,38</t>
+          <t>-1,12; 1,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 4,78</t>
+          <t>-0,57; 4,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,21</t>
+          <t>-1,08; 1,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,84</t>
+          <t>-0,49; 0,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,17</t>
+          <t>-0,15; 1,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 0,65</t>
+          <t>-0,23; 0,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 1,17</t>
+          <t>-0,02; 1,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-74,48; —</t>
+          <t>-67,04; 1095,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,48</t>
+          <t>0,2; 2,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,59</t>
+          <t>-2,01; 0,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,96</t>
+          <t>-0,43; 0,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 0,02</t>
+          <t>-3,46; 0,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 0,47</t>
+          <t>-2,04; 0,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,89</t>
+          <t>-1,48; 0,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,18</t>
+          <t>0,17; 1,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,62</t>
+          <t>-0,15; 0,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1270,32 +1270,32 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 0,31</t>
+          <t>-0,17; 0,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,27</t>
+          <t>-0,43; 0,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-32,24; 302,38</t>
+          <t>-35,94; 253,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-54,18; 112,28</t>
+          <t>-56,07; 100,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-78,08; 573,39</t>
+          <t>-79,38; 687,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-61,18; 120,18</t>
+          <t>-63,79; 116,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C08-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P19C08-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-8,16%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 0,9</t>
+          <t>-1,32; 0,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 0,17</t>
+          <t>-3,28; 0,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,0</t>
+          <t>-1,38; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,6</t>
+          <t>-0,84; 0,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 457,74</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>44,63%</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 2,64</t>
+          <t>-0,55; 2,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,26</t>
+          <t>-0,79; 1,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,19</t>
+          <t>-0,53; 1,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-82,31; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>-0,59</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-38,95%</t>
+          <t>-62,4%</t>
         </is>
       </c>
     </row>
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 1,31</t>
+          <t>-0,76; 1,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 4,72</t>
+          <t>-0,56; 4,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,27</t>
+          <t>-1,68; 0,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>373,44%</t>
+          <t>73,8%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,68</t>
+          <t>-0,54; 0,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 1,28</t>
+          <t>-0,18; 1,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 0,67</t>
+          <t>-0,23; 0,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 1,07</t>
+          <t>-0,5; 0,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-67,04; 1095,68</t>
+          <t>-68,03; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,98</t>
+          <t>-0,68</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-90,62%</t>
+          <t>-79,5%</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,32</t>
+          <t>0,2; 2,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,52</t>
+          <t>-1,95; 0,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 0,02</t>
+          <t>-3,51; 0,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 202,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,48</t>
+          <t>-1,74; 0,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,91</t>
+          <t>-1,54; 0,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,11</t>
+          <t>0,23; 1,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-7,2%</t>
+          <t>-9,61%</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,54</t>
+          <t>-0,13; 0,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,39</t>
+          <t>-0,47; 0,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1275,27 +1275,27 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,28</t>
+          <t>-0,48; 0,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-35,94; 253,43</t>
+          <t>-28,68; 299,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-56,07; 100,6</t>
+          <t>-55,1; 92,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-79,38; 687,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-63,79; 116,39</t>
+          <t>-57,95; 105,01</t>
         </is>
       </c>
     </row>
